--- a/tests/fixtures/input/peserta_testing.xlsx
+++ b/tests/fixtures/input/peserta_testing.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,27 +436,22 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Jenis Kelamin</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>NIM</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Prodi</t>
-        </is>
-      </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Kelas Umum</t>
+          <t>Kelas PAI</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Kode Kelas PAI</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Dosen Pengampu</t>
+          <t>Program Studi</t>
         </is>
       </c>
     </row>
@@ -468,27 +463,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>240001</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>1A</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>Teknik Informatika</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>TI-A</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>1A</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Dr. Ana</t>
         </is>
       </c>
     </row>
@@ -500,27 +490,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>240002</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>1A</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
         <is>
           <t>Teknik Informatika</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>TI-A</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>1A</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Dr. Ana</t>
         </is>
       </c>
     </row>
@@ -532,27 +517,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>240003</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2B</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
         <is>
           <t>Sistem Informasi</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>SI-B</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2B</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Dr. Bima</t>
         </is>
       </c>
     </row>
@@ -564,27 +544,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>240004</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2B</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
         <is>
           <t>Sistem Informasi</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>SI-B</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2B</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Dr. Bima</t>
         </is>
       </c>
     </row>
@@ -596,27 +571,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>240005</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>10A</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
         <is>
           <t>Manajemen</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>MN-A</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>10A</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Dr. Citra</t>
         </is>
       </c>
     </row>
@@ -628,27 +598,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>240006</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>10A</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
         <is>
           <t>Manajemen</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>MN-A</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>10A</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Dr. Citra</t>
         </is>
       </c>
     </row>
@@ -660,27 +625,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
           <t>240006</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>10A</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
         <is>
           <t>Manajemen</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>MN-A</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>10A</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Dr. Citra</t>
         </is>
       </c>
     </row>
